--- a/artfynd/A 10318-2025 artfynd.xlsx
+++ b/artfynd/A 10318-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,218 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123800284</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78165</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>721105</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7546438</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123800119</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78165</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>721023</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7546515</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10318-2025 artfynd.xlsx
+++ b/artfynd/A 10318-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123774006</v>
       </c>
       <c r="B2" t="n">
-        <v>57598</v>
+        <v>57601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123800284</v>
+        <v>123800119</v>
       </c>
       <c r="B3" t="n">
-        <v>78165</v>
+        <v>78170</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721105</v>
+        <v>721023</v>
       </c>
       <c r="R3" t="n">
-        <v>7546438</v>
+        <v>7546515</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -886,17 +886,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123800119</v>
+        <v>123800284</v>
       </c>
       <c r="B4" t="n">
-        <v>78165</v>
+        <v>78170</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721023</v>
+        <v>721105</v>
       </c>
       <c r="R4" t="n">
-        <v>7546515</v>
+        <v>7546438</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>

--- a/artfynd/A 10318-2025 artfynd.xlsx
+++ b/artfynd/A 10318-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123774006</v>
       </c>
       <c r="B2" t="n">
-        <v>57601</v>
+        <v>57602</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123800119</v>
+        <v>123800074</v>
       </c>
       <c r="B3" t="n">
-        <v>78170</v>
+        <v>78172</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd, Stefan Andersson</t>
+          <t>Stefan Andersson, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -896,7 +896,7 @@
         <v>123800284</v>
       </c>
       <c r="B4" t="n">
-        <v>78170</v>
+        <v>78172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 10318-2025 artfynd.xlsx
+++ b/artfynd/A 10318-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123800074</v>
+        <v>123800284</v>
       </c>
       <c r="B3" t="n">
         <v>78172</v>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721023</v>
+        <v>721105</v>
       </c>
       <c r="R3" t="n">
-        <v>7546515</v>
+        <v>7546438</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123800284</v>
+        <v>123800119</v>
       </c>
       <c r="B4" t="n">
         <v>78172</v>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721105</v>
+        <v>721023</v>
       </c>
       <c r="R4" t="n">
-        <v>7546438</v>
+        <v>7546515</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 10318-2025 artfynd.xlsx
+++ b/artfynd/A 10318-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123800284</v>
+        <v>123800119</v>
       </c>
       <c r="B3" t="n">
         <v>78172</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721105</v>
+        <v>721023</v>
       </c>
       <c r="R3" t="n">
-        <v>7546438</v>
+        <v>7546515</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123800119</v>
+        <v>123800284</v>
       </c>
       <c r="B4" t="n">
         <v>78172</v>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721023</v>
+        <v>721105</v>
       </c>
       <c r="R4" t="n">
-        <v>7546515</v>
+        <v>7546438</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 10318-2025 artfynd.xlsx
+++ b/artfynd/A 10318-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123800119</v>
+        <v>123800284</v>
       </c>
       <c r="B3" t="n">
         <v>78172</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721023</v>
+        <v>721105</v>
       </c>
       <c r="R3" t="n">
-        <v>7546515</v>
+        <v>7546438</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123800284</v>
+        <v>123800119</v>
       </c>
       <c r="B4" t="n">
         <v>78172</v>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721105</v>
+        <v>721023</v>
       </c>
       <c r="R4" t="n">
-        <v>7546438</v>
+        <v>7546515</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 10318-2025 artfynd.xlsx
+++ b/artfynd/A 10318-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123800119</v>
+        <v>123800284</v>
       </c>
       <c r="B3" t="n">
         <v>78194</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721023</v>
+        <v>721105</v>
       </c>
       <c r="R3" t="n">
-        <v>7546515</v>
+        <v>7546438</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123800284</v>
+        <v>123800074</v>
       </c>
       <c r="B4" t="n">
         <v>78194</v>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721105</v>
+        <v>721023</v>
       </c>
       <c r="R4" t="n">
-        <v>7546438</v>
+        <v>7546515</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 10318-2025 artfynd.xlsx
+++ b/artfynd/A 10318-2025 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>126983842</v>
       </c>
       <c r="B5" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>126985516</v>
       </c>
       <c r="B6" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>126985576</v>
       </c>
       <c r="B7" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>126983833</v>
       </c>
       <c r="B8" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,32 +1519,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126985528</v>
+        <v>126985575</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>91580</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720838</v>
+        <v>720640</v>
       </c>
       <c r="R10" t="n">
-        <v>7546537</v>
+        <v>7546511</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1599,12 +1599,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i gammal tall</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,45 +1626,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126985575</v>
+        <v>126983841</v>
       </c>
       <c r="B11" t="n">
-        <v>91506</v>
+        <v>78678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söder om Ylisaarenjänkkä, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720640</v>
+        <v>721088</v>
       </c>
       <c r="R11" t="n">
-        <v>7546511</v>
+        <v>7546351</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,19 +1694,9 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1726,12 +1711,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1741,7 +1726,7 @@
         <v>126985583</v>
       </c>
       <c r="B12" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126983841</v>
+        <v>126985528</v>
       </c>
       <c r="B13" t="n">
-        <v>78647</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,34 +1841,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Söder om Ylisaarenjänkkä, T lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721088</v>
+        <v>720838</v>
       </c>
       <c r="R13" t="n">
-        <v>7546351</v>
+        <v>7546537</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,9 +1898,24 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i gammal tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,44 +1930,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126983838</v>
+        <v>126983836</v>
       </c>
       <c r="B14" t="n">
-        <v>57761</v>
+        <v>79629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720885</v>
+        <v>720679</v>
       </c>
       <c r="R14" t="n">
-        <v>7546541</v>
+        <v>7546778</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,32 +2039,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126983836</v>
+        <v>126983838</v>
       </c>
       <c r="B15" t="n">
-        <v>79598</v>
+        <v>57761</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720679</v>
+        <v>720885</v>
       </c>
       <c r="R15" t="n">
-        <v>7546778</v>
+        <v>7546541</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,7 +2139,7 @@
         <v>126985521</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>126985578</v>
       </c>
       <c r="B17" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126985524</v>
+        <v>126985523</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>79629</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720842</v>
+        <v>721167</v>
       </c>
       <c r="R18" t="n">
-        <v>7546777</v>
+        <v>7546433</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2430,12 +2430,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i gammal tall</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,10 +2457,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126985574</v>
+        <v>126985573</v>
       </c>
       <c r="B19" t="n">
-        <v>91506</v>
+        <v>91480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2473,21 +2468,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>1503</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2497,10 +2492,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720659</v>
+        <v>721050</v>
       </c>
       <c r="R19" t="n">
-        <v>7546712</v>
+        <v>7546666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2532,7 +2527,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2542,7 +2537,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2569,32 +2564,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126985523</v>
+        <v>126985574</v>
       </c>
       <c r="B20" t="n">
-        <v>79598</v>
+        <v>91580</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2599,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721167</v>
+        <v>720659</v>
       </c>
       <c r="R20" t="n">
-        <v>7546433</v>
+        <v>7546712</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2639,7 +2634,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2649,7 +2644,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2676,32 +2671,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126985573</v>
+        <v>126985524</v>
       </c>
       <c r="B21" t="n">
-        <v>91406</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2711,10 +2706,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721050</v>
+        <v>720842</v>
       </c>
       <c r="R21" t="n">
-        <v>7546666</v>
+        <v>7546777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2746,7 +2741,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2756,7 +2751,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i gammal tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2786,7 +2786,7 @@
         <v>126985518</v>
       </c>
       <c r="B22" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>126985581</v>
       </c>
       <c r="B23" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>126985582</v>
       </c>
       <c r="B24" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3104,32 +3104,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126985530</v>
+        <v>126985572</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>91480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721064</v>
+        <v>721170</v>
       </c>
       <c r="R25" t="n">
-        <v>7546413</v>
+        <v>7546903</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3184,12 +3184,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>gamla ringhack i äldre tall</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,7 +3214,7 @@
         <v>126985515</v>
       </c>
       <c r="B26" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3323,7 +3318,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126985527</v>
+        <v>126985530</v>
       </c>
       <c r="B27" t="n">
         <v>57657</v>
@@ -3358,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720707</v>
+        <v>721064</v>
       </c>
       <c r="R27" t="n">
-        <v>7546752</v>
+        <v>7546413</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3393,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3403,12 +3398,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhadk i gammal tall</t>
+          <t>gamla ringhack i äldre tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,32 +3430,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126985572</v>
+        <v>126985527</v>
       </c>
       <c r="B28" t="n">
-        <v>91406</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3470,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721170</v>
+        <v>720707</v>
       </c>
       <c r="R28" t="n">
-        <v>7546903</v>
+        <v>7546752</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3505,7 +3500,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3515,7 +3510,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhadk i gammal tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,7 +3545,7 @@
         <v>126985517</v>
       </c>
       <c r="B29" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>126983831</v>
       </c>
       <c r="B30" t="n">
-        <v>91167</v>
+        <v>91241</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126985522</v>
       </c>
       <c r="B31" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>126985513</v>
       </c>
       <c r="B32" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126985577</v>
+        <v>126983839</v>
       </c>
       <c r="B33" t="n">
-        <v>78386</v>
+        <v>79090</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3971,34 +3971,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Söder om Ylisaarenjänkkä, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720823</v>
+        <v>720891</v>
       </c>
       <c r="R33" t="n">
-        <v>7546825</v>
+        <v>7547164</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4028,19 +4028,9 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4055,22 +4045,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126983839</v>
+        <v>126985577</v>
       </c>
       <c r="B34" t="n">
-        <v>79059</v>
+        <v>78417</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,34 +4068,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Söder om Ylisaarenjänkkä, T lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720891</v>
+        <v>720823</v>
       </c>
       <c r="R34" t="n">
-        <v>7547164</v>
+        <v>7546825</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4135,9 +4125,19 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4152,12 +4152,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4167,7 +4167,7 @@
         <v>126985520</v>
       </c>
       <c r="B35" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>126985514</v>
       </c>
       <c r="B36" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>126985580</v>
       </c>
       <c r="B37" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>126983835</v>
       </c>
       <c r="B38" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4582,10 +4582,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126985512</v>
+        <v>126983832</v>
       </c>
       <c r="B39" t="n">
-        <v>91167</v>
+        <v>79629</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4593,34 +4593,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Söder om Ylisaarenjänkkä, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720652</v>
+        <v>720693</v>
       </c>
       <c r="R39" t="n">
-        <v>7546599</v>
+        <v>7546693</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4650,19 +4650,9 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4677,22 +4667,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126983832</v>
+        <v>126985512</v>
       </c>
       <c r="B40" t="n">
-        <v>79598</v>
+        <v>91241</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4700,34 +4690,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Söder om Ylisaarenjänkkä, T lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720693</v>
+        <v>720652</v>
       </c>
       <c r="R40" t="n">
-        <v>7546693</v>
+        <v>7546599</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4757,9 +4747,19 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4774,12 +4774,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 10318-2025 artfynd.xlsx
+++ b/artfynd/A 10318-2025 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>126983842</v>
       </c>
       <c r="B5" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>126985516</v>
       </c>
       <c r="B6" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>126985576</v>
       </c>
       <c r="B7" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>126983833</v>
       </c>
       <c r="B8" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,32 +1519,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126985575</v>
+        <v>126985583</v>
       </c>
       <c r="B10" t="n">
-        <v>91580</v>
+        <v>78420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720640</v>
+        <v>721053</v>
       </c>
       <c r="R10" t="n">
-        <v>7546511</v>
+        <v>7546411</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,45 +1626,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126983841</v>
+        <v>126985575</v>
       </c>
       <c r="B11" t="n">
-        <v>78678</v>
+        <v>91586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Söder om Ylisaarenjänkkä, T lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721088</v>
+        <v>720640</v>
       </c>
       <c r="R11" t="n">
-        <v>7546351</v>
+        <v>7546511</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,9 +1694,19 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1711,22 +1721,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126985583</v>
+        <v>126983841</v>
       </c>
       <c r="B12" t="n">
-        <v>78417</v>
+        <v>78681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1734,34 +1744,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Söder om Ylisaarenjänkkä, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721053</v>
+        <v>721088</v>
       </c>
       <c r="R12" t="n">
-        <v>7546411</v>
+        <v>7546351</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,19 +1801,9 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1818,12 +1818,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>126983836</v>
       </c>
       <c r="B14" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>126985521</v>
       </c>
       <c r="B16" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>126985578</v>
       </c>
       <c r="B17" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>126985523</v>
       </c>
       <c r="B18" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,32 +2457,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126985573</v>
+        <v>126985524</v>
       </c>
       <c r="B19" t="n">
-        <v>91480</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721050</v>
+        <v>720842</v>
       </c>
       <c r="R19" t="n">
-        <v>7546666</v>
+        <v>7546777</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2537,7 +2537,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i gammal tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,7 +2572,7 @@
         <v>126985574</v>
       </c>
       <c r="B20" t="n">
-        <v>91580</v>
+        <v>91586</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2671,32 +2676,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126985524</v>
+        <v>126985573</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>91486</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2706,10 +2711,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720842</v>
+        <v>721050</v>
       </c>
       <c r="R21" t="n">
-        <v>7546777</v>
+        <v>7546666</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2741,7 +2746,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2751,12 +2756,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i gammal tall</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2786,7 +2786,7 @@
         <v>126985518</v>
       </c>
       <c r="B22" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>126985581</v>
       </c>
       <c r="B23" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>126985582</v>
       </c>
       <c r="B24" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3104,32 +3104,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126985572</v>
+        <v>126985515</v>
       </c>
       <c r="B25" t="n">
-        <v>91480</v>
+        <v>79632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721170</v>
+        <v>721208</v>
       </c>
       <c r="R25" t="n">
-        <v>7546903</v>
+        <v>7546617</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3211,32 +3211,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126985515</v>
+        <v>126985572</v>
       </c>
       <c r="B26" t="n">
-        <v>79629</v>
+        <v>91486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721208</v>
+        <v>721170</v>
       </c>
       <c r="R26" t="n">
-        <v>7546617</v>
+        <v>7546903</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,10 +3542,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126985517</v>
+        <v>126983831</v>
       </c>
       <c r="B29" t="n">
-        <v>79629</v>
+        <v>91247</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3553,34 +3553,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Söder om Ylisaarenjänkkä, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720829</v>
+        <v>721080</v>
       </c>
       <c r="R29" t="n">
-        <v>7546815</v>
+        <v>7546963</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,19 +3610,9 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3637,22 +3627,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126983831</v>
+        <v>126985517</v>
       </c>
       <c r="B30" t="n">
-        <v>91241</v>
+        <v>79632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3660,34 +3650,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Söder om Ylisaarenjänkkä, T lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721080</v>
+        <v>720829</v>
       </c>
       <c r="R30" t="n">
-        <v>7546963</v>
+        <v>7546815</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,9 +3707,19 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3734,12 +3734,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3749,7 +3749,7 @@
         <v>126985522</v>
       </c>
       <c r="B31" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>126985513</v>
       </c>
       <c r="B32" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126983839</v>
+        <v>126985577</v>
       </c>
       <c r="B33" t="n">
-        <v>79090</v>
+        <v>78420</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3971,34 +3971,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Söder om Ylisaarenjänkkä, T lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720891</v>
+        <v>720823</v>
       </c>
       <c r="R33" t="n">
-        <v>7547164</v>
+        <v>7546825</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4028,9 +4028,19 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4045,22 +4055,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126985577</v>
+        <v>126983839</v>
       </c>
       <c r="B34" t="n">
-        <v>78417</v>
+        <v>79093</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4068,34 +4078,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Söder om Ylisaarenjänkkä, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720823</v>
+        <v>720891</v>
       </c>
       <c r="R34" t="n">
-        <v>7546825</v>
+        <v>7547164</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4125,19 +4135,9 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4152,12 +4152,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4167,7 +4167,7 @@
         <v>126985520</v>
       </c>
       <c r="B35" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>126985514</v>
       </c>
       <c r="B36" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>126985580</v>
       </c>
       <c r="B37" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>126983835</v>
       </c>
       <c r="B38" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>126983832</v>
       </c>
       <c r="B39" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>126985512</v>
       </c>
       <c r="B40" t="n">
-        <v>91241</v>
+        <v>91247</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 10318-2025 artfynd.xlsx
+++ b/artfynd/A 10318-2025 artfynd.xlsx
@@ -1519,32 +1519,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126985583</v>
+        <v>126985575</v>
       </c>
       <c r="B10" t="n">
-        <v>78420</v>
+        <v>91586</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721053</v>
+        <v>720640</v>
       </c>
       <c r="R10" t="n">
-        <v>7546411</v>
+        <v>7546511</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,45 +1626,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126985575</v>
+        <v>126983841</v>
       </c>
       <c r="B11" t="n">
-        <v>91586</v>
+        <v>78681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söder om Ylisaarenjänkkä, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720640</v>
+        <v>721088</v>
       </c>
       <c r="R11" t="n">
-        <v>7546511</v>
+        <v>7546351</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,19 +1694,9 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,22 +1711,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126983841</v>
+        <v>126985528</v>
       </c>
       <c r="B12" t="n">
-        <v>78681</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,34 +1734,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Söder om Ylisaarenjänkkä, T lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721088</v>
+        <v>720838</v>
       </c>
       <c r="R12" t="n">
-        <v>7546351</v>
+        <v>7546537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,9 +1791,24 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i gammal tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1818,22 +1823,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126985528</v>
+        <v>126985583</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>78420</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1841,21 +1846,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720838</v>
+        <v>721053</v>
       </c>
       <c r="R13" t="n">
-        <v>7546537</v>
+        <v>7546411</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,7 +1905,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1910,12 +1915,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i gammal tall</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,32 +1942,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126983836</v>
+        <v>126983838</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>57761</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720679</v>
+        <v>720885</v>
       </c>
       <c r="R14" t="n">
-        <v>7546778</v>
+        <v>7546541</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,32 +2039,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126983838</v>
+        <v>126983836</v>
       </c>
       <c r="B15" t="n">
-        <v>57761</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720885</v>
+        <v>720679</v>
       </c>
       <c r="R15" t="n">
-        <v>7546541</v>
+        <v>7546778</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126985523</v>
+        <v>126985524</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721167</v>
+        <v>720842</v>
       </c>
       <c r="R18" t="n">
-        <v>7546433</v>
+        <v>7546777</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2430,7 +2430,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i gammal tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2457,10 +2462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126985524</v>
+        <v>126985523</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2468,21 +2473,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2492,10 +2497,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720842</v>
+        <v>721167</v>
       </c>
       <c r="R19" t="n">
-        <v>7546777</v>
+        <v>7546433</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,7 +2532,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2537,12 +2542,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack i gammal tall</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3104,32 +3104,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126985515</v>
+        <v>126985572</v>
       </c>
       <c r="B25" t="n">
-        <v>79632</v>
+        <v>91486</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721208</v>
+        <v>721170</v>
       </c>
       <c r="R25" t="n">
-        <v>7546617</v>
+        <v>7546903</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3211,32 +3211,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126985572</v>
+        <v>126985530</v>
       </c>
       <c r="B26" t="n">
-        <v>91486</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721170</v>
+        <v>721064</v>
       </c>
       <c r="R26" t="n">
-        <v>7546903</v>
+        <v>7546413</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>gamla ringhack i äldre tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,7 +3323,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126985530</v>
+        <v>126985527</v>
       </c>
       <c r="B27" t="n">
         <v>57657</v>
@@ -3353,10 +3358,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721064</v>
+        <v>720707</v>
       </c>
       <c r="R27" t="n">
-        <v>7546413</v>
+        <v>7546752</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3393,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,12 +3403,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>gamla ringhack i äldre tall</t>
+          <t>Äldre ringhadk i gammal tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126985527</v>
+        <v>126985515</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,21 +3446,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3465,10 +3470,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720707</v>
+        <v>721208</v>
       </c>
       <c r="R28" t="n">
-        <v>7546752</v>
+        <v>7546617</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3500,7 +3505,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3510,12 +3515,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhadk i gammal tall</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3542,10 +3542,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126983831</v>
+        <v>126985517</v>
       </c>
       <c r="B29" t="n">
-        <v>91247</v>
+        <v>79632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3553,34 +3553,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Söder om Ylisaarenjänkkä, T lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721080</v>
+        <v>720829</v>
       </c>
       <c r="R29" t="n">
-        <v>7546963</v>
+        <v>7546815</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,9 +3610,19 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3627,22 +3637,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126985517</v>
+        <v>126983831</v>
       </c>
       <c r="B30" t="n">
-        <v>79632</v>
+        <v>91247</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,34 +3660,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Söder om Ylisaarenjänkkä, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720829</v>
+        <v>721080</v>
       </c>
       <c r="R30" t="n">
-        <v>7546815</v>
+        <v>7546963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3707,19 +3717,9 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3734,12 +3734,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3960,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126985577</v>
+        <v>126983839</v>
       </c>
       <c r="B33" t="n">
-        <v>78420</v>
+        <v>79093</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3971,34 +3971,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Söder om Ylisaarenjänkkä, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720823</v>
+        <v>720891</v>
       </c>
       <c r="R33" t="n">
-        <v>7546825</v>
+        <v>7547164</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4028,19 +4028,9 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4055,22 +4045,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126983839</v>
+        <v>126985577</v>
       </c>
       <c r="B34" t="n">
-        <v>79093</v>
+        <v>78420</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,34 +4068,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Söder om Ylisaarenjänkkä, T lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720891</v>
+        <v>720823</v>
       </c>
       <c r="R34" t="n">
-        <v>7547164</v>
+        <v>7546825</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4135,9 +4125,19 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4152,12 +4152,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4582,10 +4582,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126983832</v>
+        <v>126985512</v>
       </c>
       <c r="B39" t="n">
-        <v>79632</v>
+        <v>91247</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4593,34 +4593,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Söder om Ylisaarenjänkkä, T lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720693</v>
+        <v>720652</v>
       </c>
       <c r="R39" t="n">
-        <v>7546693</v>
+        <v>7546599</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4650,9 +4650,19 @@
           <t>2025-07-28</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4667,22 +4677,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126985512</v>
+        <v>126983832</v>
       </c>
       <c r="B40" t="n">
-        <v>91247</v>
+        <v>79632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4690,34 +4700,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Söder om Ylisaarenjänkkä, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720652</v>
+        <v>720693</v>
       </c>
       <c r="R40" t="n">
-        <v>7546599</v>
+        <v>7546693</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4747,19 +4757,9 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4774,12 +4774,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 10318-2025 artfynd.xlsx
+++ b/artfynd/A 10318-2025 artfynd.xlsx
@@ -1942,32 +1942,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126983838</v>
+        <v>126983836</v>
       </c>
       <c r="B14" t="n">
-        <v>57761</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720885</v>
+        <v>720679</v>
       </c>
       <c r="R14" t="n">
-        <v>7546541</v>
+        <v>7546778</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,32 +2039,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126983836</v>
+        <v>126983838</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>57761</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720679</v>
+        <v>720885</v>
       </c>
       <c r="R15" t="n">
-        <v>7546778</v>
+        <v>7546541</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
